--- a/spreadsheet/Grass_data_weekly_2009-2024.xlsx
+++ b/spreadsheet/Grass_data_weekly_2009-2024.xlsx
@@ -2920,7 +2920,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>30.91777619836039</v>
+        <v>6.854528968943185</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>31.37669998250232</v>
+        <v>7.03368572754606</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>31.83562376664426</v>
+        <v>7.518983528026097</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>32.29454755078619</v>
+        <v>8.425623627772788</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>32.75347133492812</v>
+        <v>9.526346614371672</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>33.21239511907006</v>
+        <v>9.975172679529194</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>33.67131890321199</v>
+        <v>11.18521807835811</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>34.13024268735393</v>
+        <v>14.22902793459837</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>34.58916647149586</v>
+        <v>17.3452111256389</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>35.0480902556378</v>
+        <v>22.38573995940518</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>35.50701403977973</v>
+        <v>28.23852898690002</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>35.96593782392166</v>
+        <v>34.8954568648472</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>36.42486160806359</v>
+        <v>45.56737149155249</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>20</v>
       </c>
       <c r="D18">
-        <v>36.88378539220552</v>
+        <v>52.46121389833615</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3158,7 +3158,7 @@
         <v>21</v>
       </c>
       <c r="D19">
-        <v>37.34270917634746</v>
+        <v>57.03478496451859</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3172,7 +3172,7 @@
         <v>22</v>
       </c>
       <c r="D20">
-        <v>37.80163296048939</v>
+        <v>62.58059496111045</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3186,7 +3186,7 @@
         <v>23</v>
       </c>
       <c r="D21">
-        <v>38.26055674463133</v>
+        <v>71.69760535869358</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3200,7 +3200,7 @@
         <v>24</v>
       </c>
       <c r="D22">
-        <v>38.71948052877326</v>
+        <v>73.97904219335875</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3214,7 +3214,7 @@
         <v>25</v>
       </c>
       <c r="D23">
-        <v>39.17840431291519</v>
+        <v>76.1336195197991</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3228,7 +3228,7 @@
         <v>26</v>
       </c>
       <c r="D24">
-        <v>39.63732809705713</v>
+        <v>69.5451984688922</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3242,7 +3242,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>40.09625188119907</v>
+        <v>65.48814501434239</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3256,7 +3256,7 @@
         <v>28</v>
       </c>
       <c r="D26">
-        <v>40.555175665341</v>
+        <v>66.4225272500118</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3270,7 +3270,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>41.01409944948293</v>
+        <v>64.03620840335277</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3284,7 +3284,7 @@
         <v>30</v>
       </c>
       <c r="D28">
-        <v>41.47302323362486</v>
+        <v>61.85817823188949</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="D29">
-        <v>41.9319470177668</v>
+        <v>60.44814623697598</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3312,7 +3312,7 @@
         <v>32</v>
       </c>
       <c r="D30">
-        <v>42.39087080190873</v>
+        <v>58.91129319455056</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3326,7 +3326,7 @@
         <v>33</v>
       </c>
       <c r="D31">
-        <v>42.84979458605066</v>
+        <v>59.81015942309325</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3340,7 +3340,7 @@
         <v>34</v>
       </c>
       <c r="D32">
-        <v>43.30871837019259</v>
+        <v>60.67431865726294</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3354,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="D33">
-        <v>43.76764215433453</v>
+        <v>61.54400339993682</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3368,7 +3368,7 @@
         <v>36</v>
       </c>
       <c r="D34">
-        <v>44.22656593847647</v>
+        <v>62.37901063599286</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3382,7 +3382,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>44.6854897226184</v>
+        <v>59.73418161014251</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3396,7 +3396,7 @@
         <v>38</v>
       </c>
       <c r="D36">
-        <v>45.14441350676033</v>
+        <v>57.10532002513312</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3410,7 +3410,7 @@
         <v>39</v>
       </c>
       <c r="D37">
-        <v>45.60333729090227</v>
+        <v>55.53225712257375</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3424,7 +3424,7 @@
         <v>40</v>
       </c>
       <c r="D38">
-        <v>46.0622610750442</v>
+        <v>55.1710781636664</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3438,7 +3438,7 @@
         <v>41</v>
       </c>
       <c r="D39">
-        <v>46.52118485918614</v>
+        <v>54.59128132978131</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3452,7 +3452,7 @@
         <v>42</v>
       </c>
       <c r="D40">
-        <v>46.98010864332807</v>
+        <v>50.76911314141653</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3466,7 +3466,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>47.43903242747</v>
+        <v>45.30115145136081</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3480,7 +3480,7 @@
         <v>44</v>
       </c>
       <c r="D42">
-        <v>47.89795621161193</v>
+        <v>38.79716532615989</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3494,7 +3494,7 @@
         <v>45</v>
       </c>
       <c r="D43">
-        <v>48.35687999575387</v>
+        <v>32.73673971861474</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3508,7 +3508,7 @@
         <v>46</v>
       </c>
       <c r="D44">
-        <v>48.8158037798958</v>
+        <v>27.5380258863943</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3522,7 +3522,7 @@
         <v>47</v>
       </c>
       <c r="D45">
-        <v>49.27472756403773</v>
+        <v>22.23751373218285</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3536,7 +3536,7 @@
         <v>48</v>
       </c>
       <c r="D46">
-        <v>49.73365134817966</v>
+        <v>18.89257931108279</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3550,7 +3550,7 @@
         <v>49</v>
       </c>
       <c r="D47">
-        <v>50.1925751323216</v>
+        <v>14.67726116105257</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3564,7 +3564,7 @@
         <v>50</v>
       </c>
       <c r="D48">
-        <v>50.65149891646354</v>
+        <v>11.80931891100816</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3578,7 +3578,7 @@
         <v>51</v>
       </c>
       <c r="D49">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3592,7 +3592,7 @@
         <v>52</v>
       </c>
       <c r="D50">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3606,7 +3606,7 @@
         <v>53</v>
       </c>
       <c r="D51">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3620,7 +3620,7 @@
         <v>54</v>
       </c>
       <c r="D52">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3634,7 +3634,7 @@
         <v>55</v>
       </c>
       <c r="D53">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3648,7 +3648,7 @@
         <v>56</v>
       </c>
       <c r="D54">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3662,7 +3662,7 @@
         <v>57</v>
       </c>
       <c r="D55">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3676,7 +3676,7 @@
         <v>58</v>
       </c>
       <c r="D56">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3690,7 +3690,7 @@
         <v>59</v>
       </c>
       <c r="D57">
-        <v>30.91777619836039</v>
+        <v>6.854528968943185</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3704,7 +3704,7 @@
         <v>60</v>
       </c>
       <c r="D58">
-        <v>31.37669998250232</v>
+        <v>7.03368572754606</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3718,7 +3718,7 @@
         <v>61</v>
       </c>
       <c r="D59">
-        <v>31.83562376664426</v>
+        <v>7.518983528026097</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3732,7 +3732,7 @@
         <v>62</v>
       </c>
       <c r="D60">
-        <v>32.29454755078619</v>
+        <v>8.425623627772788</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3746,7 +3746,7 @@
         <v>63</v>
       </c>
       <c r="D61">
-        <v>32.75347133492812</v>
+        <v>9.526346614371672</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3760,7 +3760,7 @@
         <v>64</v>
       </c>
       <c r="D62">
-        <v>33.21239511907006</v>
+        <v>9.975172679529194</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3774,7 +3774,7 @@
         <v>65</v>
       </c>
       <c r="D63">
-        <v>33.67131890321199</v>
+        <v>11.18521807835811</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3788,7 +3788,7 @@
         <v>66</v>
       </c>
       <c r="D64">
-        <v>34.13024268735393</v>
+        <v>14.22902793459837</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3802,7 +3802,7 @@
         <v>67</v>
       </c>
       <c r="D65">
-        <v>34.58916647149586</v>
+        <v>17.3452111256389</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3816,7 +3816,7 @@
         <v>68</v>
       </c>
       <c r="D66">
-        <v>35.0480902556378</v>
+        <v>22.38573995940518</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3830,7 +3830,7 @@
         <v>69</v>
       </c>
       <c r="D67">
-        <v>35.50701403977973</v>
+        <v>28.23852898690002</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3844,7 +3844,7 @@
         <v>70</v>
       </c>
       <c r="D68">
-        <v>35.96593782392166</v>
+        <v>34.8954568648472</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3858,7 +3858,7 @@
         <v>71</v>
       </c>
       <c r="D69">
-        <v>36.42486160806359</v>
+        <v>45.56737149155249</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3872,7 +3872,7 @@
         <v>72</v>
       </c>
       <c r="D70">
-        <v>36.88378539220552</v>
+        <v>52.46121389833615</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3886,7 +3886,7 @@
         <v>73</v>
       </c>
       <c r="D71">
-        <v>37.34270917634746</v>
+        <v>57.03478496451859</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3900,7 +3900,7 @@
         <v>74</v>
       </c>
       <c r="D72">
-        <v>37.80163296048939</v>
+        <v>62.58059496111045</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3914,7 +3914,7 @@
         <v>75</v>
       </c>
       <c r="D73">
-        <v>38.26055674463133</v>
+        <v>71.69760535869358</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3928,7 +3928,7 @@
         <v>76</v>
       </c>
       <c r="D74">
-        <v>38.71948052877326</v>
+        <v>73.97904219335875</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3942,7 +3942,7 @@
         <v>77</v>
       </c>
       <c r="D75">
-        <v>39.17840431291519</v>
+        <v>76.1336195197991</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3956,7 +3956,7 @@
         <v>78</v>
       </c>
       <c r="D76">
-        <v>39.63732809705713</v>
+        <v>69.5451984688922</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3970,7 +3970,7 @@
         <v>79</v>
       </c>
       <c r="D77">
-        <v>40.09625188119907</v>
+        <v>65.48814501434239</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3984,7 +3984,7 @@
         <v>80</v>
       </c>
       <c r="D78">
-        <v>40.555175665341</v>
+        <v>66.4225272500118</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3998,7 +3998,7 @@
         <v>81</v>
       </c>
       <c r="D79">
-        <v>41.01409944948293</v>
+        <v>64.03620840335277</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -4012,7 +4012,7 @@
         <v>82</v>
       </c>
       <c r="D80">
-        <v>41.47302323362486</v>
+        <v>61.85817823188949</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -4026,7 +4026,7 @@
         <v>83</v>
       </c>
       <c r="D81">
-        <v>41.9319470177668</v>
+        <v>60.44814623697598</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4040,7 +4040,7 @@
         <v>84</v>
       </c>
       <c r="D82">
-        <v>42.39087080190873</v>
+        <v>58.91129319455056</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4054,7 +4054,7 @@
         <v>85</v>
       </c>
       <c r="D83">
-        <v>42.84979458605066</v>
+        <v>59.81015942309325</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -4068,7 +4068,7 @@
         <v>86</v>
       </c>
       <c r="D84">
-        <v>43.30871837019259</v>
+        <v>60.67431865726294</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -4082,7 +4082,7 @@
         <v>87</v>
       </c>
       <c r="D85">
-        <v>43.76764215433453</v>
+        <v>61.54400339993682</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -4096,7 +4096,7 @@
         <v>88</v>
       </c>
       <c r="D86">
-        <v>44.22656593847647</v>
+        <v>62.37901063599286</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -4110,7 +4110,7 @@
         <v>89</v>
       </c>
       <c r="D87">
-        <v>44.6854897226184</v>
+        <v>59.73418161014251</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -4124,7 +4124,7 @@
         <v>90</v>
       </c>
       <c r="D88">
-        <v>45.14441350676033</v>
+        <v>57.10532002513312</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -4138,7 +4138,7 @@
         <v>91</v>
       </c>
       <c r="D89">
-        <v>45.60333729090227</v>
+        <v>55.53225712257375</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4152,7 +4152,7 @@
         <v>92</v>
       </c>
       <c r="D90">
-        <v>46.0622610750442</v>
+        <v>55.1710781636664</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -4166,7 +4166,7 @@
         <v>93</v>
       </c>
       <c r="D91">
-        <v>46.52118485918614</v>
+        <v>54.59128132978131</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -4180,7 +4180,7 @@
         <v>94</v>
       </c>
       <c r="D92">
-        <v>46.98010864332807</v>
+        <v>50.76911314141653</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4194,7 +4194,7 @@
         <v>95</v>
       </c>
       <c r="D93">
-        <v>47.43903242747</v>
+        <v>45.30115145136081</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4208,7 +4208,7 @@
         <v>96</v>
       </c>
       <c r="D94">
-        <v>47.89795621161193</v>
+        <v>38.79716532615989</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4222,7 +4222,7 @@
         <v>97</v>
       </c>
       <c r="D95">
-        <v>48.35687999575387</v>
+        <v>32.73673971861474</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -4236,7 +4236,7 @@
         <v>98</v>
       </c>
       <c r="D96">
-        <v>48.8158037798958</v>
+        <v>27.5380258863943</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -4250,7 +4250,7 @@
         <v>99</v>
       </c>
       <c r="D97">
-        <v>49.27472756403773</v>
+        <v>22.23751373218285</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4264,7 +4264,7 @@
         <v>100</v>
       </c>
       <c r="D98">
-        <v>49.73365134817966</v>
+        <v>18.89257931108279</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4278,7 +4278,7 @@
         <v>101</v>
       </c>
       <c r="D99">
-        <v>50.1925751323216</v>
+        <v>14.67726116105257</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -4292,7 +4292,7 @@
         <v>102</v>
       </c>
       <c r="D100">
-        <v>50.65149891646354</v>
+        <v>11.80931891100816</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -4306,7 +4306,7 @@
         <v>103</v>
       </c>
       <c r="D101">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -4320,7 +4320,7 @@
         <v>104</v>
       </c>
       <c r="D102">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -4334,7 +4334,7 @@
         <v>105</v>
       </c>
       <c r="D103">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4348,7 +4348,7 @@
         <v>106</v>
       </c>
       <c r="D104">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4362,7 +4362,7 @@
         <v>107</v>
       </c>
       <c r="D105">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4376,7 +4376,7 @@
         <v>108</v>
       </c>
       <c r="D106">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4390,7 +4390,7 @@
         <v>109</v>
       </c>
       <c r="D107">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4404,7 +4404,7 @@
         <v>110</v>
       </c>
       <c r="D108">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4418,7 +4418,7 @@
         <v>111</v>
       </c>
       <c r="D109">
-        <v>30.91777619836039</v>
+        <v>6.854528968943185</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4432,7 +4432,7 @@
         <v>112</v>
       </c>
       <c r="D110">
-        <v>31.37669998250232</v>
+        <v>7.03368572754606</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4446,7 +4446,7 @@
         <v>113</v>
       </c>
       <c r="D111">
-        <v>31.83562376664426</v>
+        <v>7.518983528026097</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4460,7 +4460,7 @@
         <v>114</v>
       </c>
       <c r="D112">
-        <v>32.29454755078619</v>
+        <v>8.425623627772788</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4474,7 +4474,7 @@
         <v>115</v>
       </c>
       <c r="D113">
-        <v>32.75347133492812</v>
+        <v>9.526346614371672</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4488,7 +4488,7 @@
         <v>116</v>
       </c>
       <c r="D114">
-        <v>33.21239511907006</v>
+        <v>9.975172679529194</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4502,7 +4502,7 @@
         <v>117</v>
       </c>
       <c r="D115">
-        <v>33.67131890321199</v>
+        <v>11.18521807835811</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4516,7 +4516,7 @@
         <v>118</v>
       </c>
       <c r="D116">
-        <v>34.13024268735393</v>
+        <v>14.22902793459837</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4530,7 +4530,7 @@
         <v>119</v>
       </c>
       <c r="D117">
-        <v>34.58916647149586</v>
+        <v>17.3452111256389</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4544,7 +4544,7 @@
         <v>120</v>
       </c>
       <c r="D118">
-        <v>35.0480902556378</v>
+        <v>22.38573995940518</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4558,7 +4558,7 @@
         <v>121</v>
       </c>
       <c r="D119">
-        <v>35.50701403977973</v>
+        <v>28.23852898690002</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4572,7 +4572,7 @@
         <v>122</v>
       </c>
       <c r="D120">
-        <v>35.96593782392166</v>
+        <v>34.8954568648472</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4586,7 +4586,7 @@
         <v>123</v>
       </c>
       <c r="D121">
-        <v>36.42486160806359</v>
+        <v>45.56737149155249</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4600,7 +4600,7 @@
         <v>124</v>
       </c>
       <c r="D122">
-        <v>36.88378539220552</v>
+        <v>52.46121389833615</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4614,7 +4614,7 @@
         <v>125</v>
       </c>
       <c r="D123">
-        <v>37.34270917634746</v>
+        <v>57.03478496451859</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4628,7 +4628,7 @@
         <v>126</v>
       </c>
       <c r="D124">
-        <v>37.80163296048939</v>
+        <v>62.58059496111045</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4642,7 +4642,7 @@
         <v>127</v>
       </c>
       <c r="D125">
-        <v>38.26055674463133</v>
+        <v>71.69760535869358</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4656,7 +4656,7 @@
         <v>128</v>
       </c>
       <c r="D126">
-        <v>38.71948052877326</v>
+        <v>73.97904219335875</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4670,7 +4670,7 @@
         <v>129</v>
       </c>
       <c r="D127">
-        <v>39.17840431291519</v>
+        <v>76.1336195197991</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4684,7 +4684,7 @@
         <v>130</v>
       </c>
       <c r="D128">
-        <v>39.63732809705713</v>
+        <v>69.5451984688922</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4698,7 +4698,7 @@
         <v>131</v>
       </c>
       <c r="D129">
-        <v>40.09625188119907</v>
+        <v>65.48814501434239</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4712,7 +4712,7 @@
         <v>132</v>
       </c>
       <c r="D130">
-        <v>40.555175665341</v>
+        <v>66.4225272500118</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4726,7 +4726,7 @@
         <v>133</v>
       </c>
       <c r="D131">
-        <v>41.01409944948293</v>
+        <v>64.03620840335277</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4740,7 +4740,7 @@
         <v>134</v>
       </c>
       <c r="D132">
-        <v>41.47302323362486</v>
+        <v>61.85817823188949</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4754,7 +4754,7 @@
         <v>135</v>
       </c>
       <c r="D133">
-        <v>41.9319470177668</v>
+        <v>60.44814623697598</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4768,7 +4768,7 @@
         <v>136</v>
       </c>
       <c r="D134">
-        <v>42.39087080190873</v>
+        <v>58.91129319455056</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4782,7 +4782,7 @@
         <v>137</v>
       </c>
       <c r="D135">
-        <v>42.84979458605066</v>
+        <v>59.81015942309325</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4796,7 +4796,7 @@
         <v>138</v>
       </c>
       <c r="D136">
-        <v>43.30871837019259</v>
+        <v>60.67431865726294</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4810,7 +4810,7 @@
         <v>139</v>
       </c>
       <c r="D137">
-        <v>43.76764215433453</v>
+        <v>61.54400339993682</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4824,7 +4824,7 @@
         <v>140</v>
       </c>
       <c r="D138">
-        <v>44.22656593847647</v>
+        <v>62.37901063599286</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4838,7 +4838,7 @@
         <v>141</v>
       </c>
       <c r="D139">
-        <v>44.6854897226184</v>
+        <v>59.73418161014251</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4852,7 +4852,7 @@
         <v>142</v>
       </c>
       <c r="D140">
-        <v>45.14441350676033</v>
+        <v>57.10532002513312</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4866,7 +4866,7 @@
         <v>143</v>
       </c>
       <c r="D141">
-        <v>45.60333729090227</v>
+        <v>55.53225712257375</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4880,7 +4880,7 @@
         <v>144</v>
       </c>
       <c r="D142">
-        <v>46.0622610750442</v>
+        <v>55.1710781636664</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4894,7 +4894,7 @@
         <v>145</v>
       </c>
       <c r="D143">
-        <v>46.52118485918614</v>
+        <v>54.59128132978131</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4908,7 +4908,7 @@
         <v>146</v>
       </c>
       <c r="D144">
-        <v>46.98010864332807</v>
+        <v>50.76911314141653</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4922,7 +4922,7 @@
         <v>147</v>
       </c>
       <c r="D145">
-        <v>47.43903242747</v>
+        <v>45.30115145136081</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4936,7 +4936,7 @@
         <v>148</v>
       </c>
       <c r="D146">
-        <v>47.89795621161193</v>
+        <v>38.79716532615989</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4950,7 +4950,7 @@
         <v>149</v>
       </c>
       <c r="D147">
-        <v>48.35687999575387</v>
+        <v>32.73673971861474</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4964,7 +4964,7 @@
         <v>150</v>
       </c>
       <c r="D148">
-        <v>48.8158037798958</v>
+        <v>27.5380258863943</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4978,7 +4978,7 @@
         <v>151</v>
       </c>
       <c r="D149">
-        <v>49.27472756403773</v>
+        <v>22.23751373218285</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4992,7 +4992,7 @@
         <v>152</v>
       </c>
       <c r="D150">
-        <v>49.73365134817966</v>
+        <v>18.89257931108279</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -5006,7 +5006,7 @@
         <v>153</v>
       </c>
       <c r="D151">
-        <v>50.1925751323216</v>
+        <v>14.67726116105257</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -5020,7 +5020,7 @@
         <v>154</v>
       </c>
       <c r="D152">
-        <v>50.65149891646354</v>
+        <v>11.80931891100816</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -5034,7 +5034,7 @@
         <v>155</v>
       </c>
       <c r="D153">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -5048,7 +5048,7 @@
         <v>156</v>
       </c>
       <c r="D154">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -5062,7 +5062,7 @@
         <v>157</v>
       </c>
       <c r="D155">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -5076,7 +5076,7 @@
         <v>158</v>
       </c>
       <c r="D156">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -5090,7 +5090,7 @@
         <v>159</v>
       </c>
       <c r="D157">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -5104,7 +5104,7 @@
         <v>160</v>
       </c>
       <c r="D158">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -5118,7 +5118,7 @@
         <v>161</v>
       </c>
       <c r="D159">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -5132,7 +5132,7 @@
         <v>162</v>
       </c>
       <c r="D160">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -5146,7 +5146,7 @@
         <v>163</v>
       </c>
       <c r="D161">
-        <v>30.91777619836039</v>
+        <v>6.854528968943185</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -5160,7 +5160,7 @@
         <v>164</v>
       </c>
       <c r="D162">
-        <v>31.37669998250232</v>
+        <v>7.03368572754606</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -5174,7 +5174,7 @@
         <v>165</v>
       </c>
       <c r="D163">
-        <v>31.83562376664426</v>
+        <v>7.518983528026097</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -5188,7 +5188,7 @@
         <v>166</v>
       </c>
       <c r="D164">
-        <v>32.29454755078619</v>
+        <v>8.425623627772788</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -5202,7 +5202,7 @@
         <v>167</v>
       </c>
       <c r="D165">
-        <v>32.75347133492812</v>
+        <v>9.526346614371672</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -5216,7 +5216,7 @@
         <v>168</v>
       </c>
       <c r="D166">
-        <v>33.21239511907006</v>
+        <v>9.975172679529194</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -5230,7 +5230,7 @@
         <v>169</v>
       </c>
       <c r="D167">
-        <v>33.67131890321199</v>
+        <v>11.18521807835811</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -5244,7 +5244,7 @@
         <v>170</v>
       </c>
       <c r="D168">
-        <v>34.13024268735393</v>
+        <v>14.22902793459837</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -5258,7 +5258,7 @@
         <v>171</v>
       </c>
       <c r="D169">
-        <v>34.58916647149586</v>
+        <v>17.3452111256389</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -5272,7 +5272,7 @@
         <v>172</v>
       </c>
       <c r="D170">
-        <v>35.0480902556378</v>
+        <v>22.38573995940518</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -5286,7 +5286,7 @@
         <v>173</v>
       </c>
       <c r="D171">
-        <v>35.50701403977973</v>
+        <v>28.23852898690002</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -5300,7 +5300,7 @@
         <v>174</v>
       </c>
       <c r="D172">
-        <v>35.96593782392166</v>
+        <v>34.8954568648472</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -5314,7 +5314,7 @@
         <v>175</v>
       </c>
       <c r="D173">
-        <v>36.42486160806359</v>
+        <v>45.56737149155249</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -5328,7 +5328,7 @@
         <v>176</v>
       </c>
       <c r="D174">
-        <v>36.88378539220552</v>
+        <v>52.46121389833615</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -5342,7 +5342,7 @@
         <v>177</v>
       </c>
       <c r="D175">
-        <v>37.34270917634746</v>
+        <v>57.03478496451859</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -5356,7 +5356,7 @@
         <v>178</v>
       </c>
       <c r="D176">
-        <v>37.80163296048939</v>
+        <v>62.58059496111045</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5370,7 +5370,7 @@
         <v>179</v>
       </c>
       <c r="D177">
-        <v>38.26055674463133</v>
+        <v>71.69760535869358</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5384,7 +5384,7 @@
         <v>180</v>
       </c>
       <c r="D178">
-        <v>38.71948052877326</v>
+        <v>73.97904219335875</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5398,7 +5398,7 @@
         <v>181</v>
       </c>
       <c r="D179">
-        <v>39.17840431291519</v>
+        <v>76.1336195197991</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5412,7 +5412,7 @@
         <v>182</v>
       </c>
       <c r="D180">
-        <v>39.63732809705713</v>
+        <v>69.5451984688922</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5426,7 +5426,7 @@
         <v>183</v>
       </c>
       <c r="D181">
-        <v>40.09625188119907</v>
+        <v>65.48814501434239</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5440,7 +5440,7 @@
         <v>184</v>
       </c>
       <c r="D182">
-        <v>40.555175665341</v>
+        <v>66.4225272500118</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5454,7 +5454,7 @@
         <v>185</v>
       </c>
       <c r="D183">
-        <v>41.01409944948293</v>
+        <v>64.03620840335277</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5468,7 +5468,7 @@
         <v>186</v>
       </c>
       <c r="D184">
-        <v>41.47302323362486</v>
+        <v>61.85817823188949</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5482,7 +5482,7 @@
         <v>187</v>
       </c>
       <c r="D185">
-        <v>41.9319470177668</v>
+        <v>60.44814623697598</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5496,7 +5496,7 @@
         <v>188</v>
       </c>
       <c r="D186">
-        <v>42.39087080190873</v>
+        <v>58.91129319455056</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5510,7 +5510,7 @@
         <v>189</v>
       </c>
       <c r="D187">
-        <v>42.84979458605066</v>
+        <v>59.81015942309325</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5524,7 +5524,7 @@
         <v>190</v>
       </c>
       <c r="D188">
-        <v>43.30871837019259</v>
+        <v>60.67431865726294</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5538,7 +5538,7 @@
         <v>191</v>
       </c>
       <c r="D189">
-        <v>43.76764215433453</v>
+        <v>61.54400339993682</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5552,7 +5552,7 @@
         <v>192</v>
       </c>
       <c r="D190">
-        <v>44.22656593847647</v>
+        <v>62.37901063599286</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5566,7 +5566,7 @@
         <v>193</v>
       </c>
       <c r="D191">
-        <v>44.6854897226184</v>
+        <v>59.73418161014251</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5580,7 +5580,7 @@
         <v>194</v>
       </c>
       <c r="D192">
-        <v>45.14441350676033</v>
+        <v>57.10532002513312</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5594,7 +5594,7 @@
         <v>195</v>
       </c>
       <c r="D193">
-        <v>45.60333729090227</v>
+        <v>55.53225712257375</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5608,7 +5608,7 @@
         <v>196</v>
       </c>
       <c r="D194">
-        <v>46.0622610750442</v>
+        <v>55.1710781636664</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5622,7 +5622,7 @@
         <v>197</v>
       </c>
       <c r="D195">
-        <v>46.52118485918614</v>
+        <v>54.59128132978131</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5636,7 +5636,7 @@
         <v>198</v>
       </c>
       <c r="D196">
-        <v>46.98010864332807</v>
+        <v>50.76911314141653</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5650,7 +5650,7 @@
         <v>199</v>
       </c>
       <c r="D197">
-        <v>47.43903242747</v>
+        <v>45.30115145136081</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5664,7 +5664,7 @@
         <v>200</v>
       </c>
       <c r="D198">
-        <v>47.89795621161193</v>
+        <v>38.79716532615989</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5678,7 +5678,7 @@
         <v>201</v>
       </c>
       <c r="D199">
-        <v>48.35687999575387</v>
+        <v>32.73673971861474</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5692,7 +5692,7 @@
         <v>202</v>
       </c>
       <c r="D200">
-        <v>48.8158037798958</v>
+        <v>27.5380258863943</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5706,7 +5706,7 @@
         <v>203</v>
       </c>
       <c r="D201">
-        <v>49.27472756403773</v>
+        <v>22.23751373218285</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5720,7 +5720,7 @@
         <v>204</v>
       </c>
       <c r="D202">
-        <v>49.73365134817966</v>
+        <v>18.89257931108279</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5734,7 +5734,7 @@
         <v>205</v>
       </c>
       <c r="D203">
-        <v>50.1925751323216</v>
+        <v>14.67726116105257</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5748,7 +5748,7 @@
         <v>206</v>
       </c>
       <c r="D204">
-        <v>50.65149891646354</v>
+        <v>11.80931891100816</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5762,7 +5762,7 @@
         <v>207</v>
       </c>
       <c r="D205">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5776,7 +5776,7 @@
         <v>208</v>
       </c>
       <c r="D206">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5790,7 +5790,7 @@
         <v>209</v>
       </c>
       <c r="D207">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5804,7 +5804,7 @@
         <v>210</v>
       </c>
       <c r="D208">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5818,7 +5818,7 @@
         <v>211</v>
       </c>
       <c r="D209">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5832,7 +5832,7 @@
         <v>212</v>
       </c>
       <c r="D210">
-        <v>53.40504162131514</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5846,7 +5846,7 @@
         <v>213</v>
       </c>
       <c r="D211">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5860,7 +5860,7 @@
         <v>214</v>
       </c>
       <c r="D212">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -6504,7 +6504,7 @@
         <v>260</v>
       </c>
       <c r="D258">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6518,7 +6518,7 @@
         <v>261</v>
       </c>
       <c r="D259">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6532,7 +6532,7 @@
         <v>262</v>
       </c>
       <c r="D260">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6546,7 +6546,7 @@
         <v>263</v>
       </c>
       <c r="D261">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -6560,7 +6560,7 @@
         <v>264</v>
       </c>
       <c r="D262">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -6574,7 +6574,7 @@
         <v>265</v>
       </c>
       <c r="D263">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6588,7 +6588,7 @@
         <v>266</v>
       </c>
       <c r="D264">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -6602,7 +6602,7 @@
         <v>267</v>
       </c>
       <c r="D265">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -7246,7 +7246,7 @@
         <v>313</v>
       </c>
       <c r="D311">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -7260,7 +7260,7 @@
         <v>314</v>
       </c>
       <c r="D312">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -7274,7 +7274,7 @@
         <v>315</v>
       </c>
       <c r="D313">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -7288,7 +7288,7 @@
         <v>316</v>
       </c>
       <c r="D314">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -7302,7 +7302,7 @@
         <v>317</v>
       </c>
       <c r="D315">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -7316,7 +7316,7 @@
         <v>318</v>
       </c>
       <c r="D316">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -7330,7 +7330,7 @@
         <v>319</v>
       </c>
       <c r="D317">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -7974,7 +7974,7 @@
         <v>365</v>
       </c>
       <c r="D363">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7988,7 +7988,7 @@
         <v>366</v>
       </c>
       <c r="D364">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -8002,7 +8002,7 @@
         <v>367</v>
       </c>
       <c r="D365">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -8016,7 +8016,7 @@
         <v>368</v>
       </c>
       <c r="D366">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -8030,7 +8030,7 @@
         <v>369</v>
       </c>
       <c r="D367">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -8044,7 +8044,7 @@
         <v>370</v>
       </c>
       <c r="D368">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -8058,7 +8058,7 @@
         <v>371</v>
       </c>
       <c r="D369">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -8702,7 +8702,7 @@
         <v>417</v>
       </c>
       <c r="D415">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -8716,7 +8716,7 @@
         <v>418</v>
       </c>
       <c r="D416">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -8730,7 +8730,7 @@
         <v>419</v>
       </c>
       <c r="D417">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -8744,7 +8744,7 @@
         <v>420</v>
       </c>
       <c r="D418">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -8758,7 +8758,7 @@
         <v>421</v>
       </c>
       <c r="D419">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -8772,7 +8772,7 @@
         <v>422</v>
       </c>
       <c r="D420">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -8786,7 +8786,7 @@
         <v>423</v>
       </c>
       <c r="D421">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -9430,7 +9430,7 @@
         <v>469</v>
       </c>
       <c r="D467">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -9444,7 +9444,7 @@
         <v>470</v>
       </c>
       <c r="D468">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -9458,7 +9458,7 @@
         <v>471</v>
       </c>
       <c r="D469">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -9472,7 +9472,7 @@
         <v>472</v>
       </c>
       <c r="D470">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -9486,7 +9486,7 @@
         <v>473</v>
       </c>
       <c r="D471">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -9500,7 +9500,7 @@
         <v>474</v>
       </c>
       <c r="D472">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -9514,7 +9514,7 @@
         <v>475</v>
       </c>
       <c r="D473">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -10158,7 +10158,7 @@
         <v>521</v>
       </c>
       <c r="D519">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -10172,7 +10172,7 @@
         <v>522</v>
       </c>
       <c r="D520">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -10186,7 +10186,7 @@
         <v>523</v>
       </c>
       <c r="D521">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -10200,7 +10200,7 @@
         <v>524</v>
       </c>
       <c r="D522">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -10214,7 +10214,7 @@
         <v>525</v>
       </c>
       <c r="D523">
-        <v>53.40504162131514</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -10228,7 +10228,7 @@
         <v>526</v>
       </c>
       <c r="D524">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -10242,7 +10242,7 @@
         <v>527</v>
       </c>
       <c r="D525">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -10886,7 +10886,7 @@
         <v>573</v>
       </c>
       <c r="D571">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10900,7 +10900,7 @@
         <v>574</v>
       </c>
       <c r="D572">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10914,7 +10914,7 @@
         <v>575</v>
       </c>
       <c r="D573">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10928,7 +10928,7 @@
         <v>576</v>
       </c>
       <c r="D574">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10942,7 +10942,7 @@
         <v>577</v>
       </c>
       <c r="D575">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10956,7 +10956,7 @@
         <v>578</v>
       </c>
       <c r="D576">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10970,7 +10970,7 @@
         <v>579</v>
       </c>
       <c r="D577">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10984,7 +10984,7 @@
         <v>580</v>
       </c>
       <c r="D578">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -11628,7 +11628,7 @@
         <v>626</v>
       </c>
       <c r="D624">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -11642,7 +11642,7 @@
         <v>627</v>
       </c>
       <c r="D625">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -11656,7 +11656,7 @@
         <v>628</v>
       </c>
       <c r="D626">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -11670,7 +11670,7 @@
         <v>629</v>
       </c>
       <c r="D627">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -11684,7 +11684,7 @@
         <v>630</v>
       </c>
       <c r="D628">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -11698,7 +11698,7 @@
         <v>631</v>
       </c>
       <c r="D629">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -11712,7 +11712,7 @@
         <v>632</v>
       </c>
       <c r="D630">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -12356,7 +12356,7 @@
         <v>678</v>
       </c>
       <c r="D676">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -12370,7 +12370,7 @@
         <v>679</v>
       </c>
       <c r="D677">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -12384,7 +12384,7 @@
         <v>680</v>
       </c>
       <c r="D678">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -12398,7 +12398,7 @@
         <v>681</v>
       </c>
       <c r="D679">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -12412,7 +12412,7 @@
         <v>682</v>
       </c>
       <c r="D680">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -12426,7 +12426,7 @@
         <v>683</v>
       </c>
       <c r="D681">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -12440,7 +12440,7 @@
         <v>684</v>
       </c>
       <c r="D682">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -13084,7 +13084,7 @@
         <v>730</v>
       </c>
       <c r="D728">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -13098,7 +13098,7 @@
         <v>731</v>
       </c>
       <c r="D729">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -13112,7 +13112,7 @@
         <v>732</v>
       </c>
       <c r="D730">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -13126,7 +13126,7 @@
         <v>733</v>
       </c>
       <c r="D731">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -13140,7 +13140,7 @@
         <v>734</v>
       </c>
       <c r="D732">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -13154,7 +13154,7 @@
         <v>735</v>
       </c>
       <c r="D733">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -13168,7 +13168,7 @@
         <v>736</v>
       </c>
       <c r="D734">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -13812,7 +13812,7 @@
         <v>782</v>
       </c>
       <c r="D780">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -13826,7 +13826,7 @@
         <v>783</v>
       </c>
       <c r="D781">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -13840,7 +13840,7 @@
         <v>784</v>
       </c>
       <c r="D782">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -13854,7 +13854,7 @@
         <v>785</v>
       </c>
       <c r="D783">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -13868,7 +13868,7 @@
         <v>786</v>
       </c>
       <c r="D784">
-        <v>29.54100484593459</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -13882,7 +13882,7 @@
         <v>787</v>
       </c>
       <c r="D785">
-        <v>29.99992863007652</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="786" spans="1:4">
@@ -13896,7 +13896,7 @@
         <v>788</v>
       </c>
       <c r="D786">
-        <v>30.45885241421846</v>
+        <v>8.646967651357356</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -14106,7 +14106,7 @@
         <v>803</v>
       </c>
       <c r="D801">
-        <v>37.34270917634746</v>
+        <v>57.03478496451859</v>
       </c>
     </row>
     <row r="802" spans="1:4">
@@ -14120,7 +14120,7 @@
         <v>804</v>
       </c>
       <c r="D802">
-        <v>37.80163296048939</v>
+        <v>62.58059496111045</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -14134,7 +14134,7 @@
         <v>805</v>
       </c>
       <c r="D803">
-        <v>38.26055674463133</v>
+        <v>71.69760535869358</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -14148,7 +14148,7 @@
         <v>806</v>
       </c>
       <c r="D804">
-        <v>38.71948052877326</v>
+        <v>73.97904219335875</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -14162,7 +14162,7 @@
         <v>807</v>
       </c>
       <c r="D805">
-        <v>39.17840431291519</v>
+        <v>76.1336195197991</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -14176,7 +14176,7 @@
         <v>808</v>
       </c>
       <c r="D806">
-        <v>39.63732809705713</v>
+        <v>69.5451984688922</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -14190,7 +14190,7 @@
         <v>809</v>
       </c>
       <c r="D807">
-        <v>40.09625188119907</v>
+        <v>65.48814501434239</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -14204,7 +14204,7 @@
         <v>810</v>
       </c>
       <c r="D808">
-        <v>40.555175665341</v>
+        <v>66.4225272500118</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -14218,7 +14218,7 @@
         <v>811</v>
       </c>
       <c r="D809">
-        <v>41.01409944948293</v>
+        <v>64.03620840335277</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -14232,7 +14232,7 @@
         <v>812</v>
       </c>
       <c r="D810">
-        <v>41.47302323362486</v>
+        <v>61.85817823188949</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -14246,7 +14246,7 @@
         <v>813</v>
       </c>
       <c r="D811">
-        <v>41.9319470177668</v>
+        <v>60.44814623697598</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -14260,7 +14260,7 @@
         <v>814</v>
       </c>
       <c r="D812">
-        <v>42.39087080190873</v>
+        <v>58.91129319455056</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -14274,7 +14274,7 @@
         <v>815</v>
       </c>
       <c r="D813">
-        <v>42.84979458605066</v>
+        <v>59.81015942309325</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -14288,7 +14288,7 @@
         <v>816</v>
       </c>
       <c r="D814">
-        <v>43.30871837019259</v>
+        <v>60.67431865726294</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -14302,7 +14302,7 @@
         <v>817</v>
       </c>
       <c r="D815">
-        <v>43.76764215433453</v>
+        <v>61.54400339993682</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -14316,7 +14316,7 @@
         <v>818</v>
       </c>
       <c r="D816">
-        <v>44.22656593847647</v>
+        <v>62.37901063599286</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -14330,7 +14330,7 @@
         <v>819</v>
       </c>
       <c r="D817">
-        <v>44.6854897226184</v>
+        <v>59.73418161014251</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -14344,7 +14344,7 @@
         <v>820</v>
       </c>
       <c r="D818">
-        <v>45.14441350676033</v>
+        <v>57.10532002513312</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -14358,7 +14358,7 @@
         <v>821</v>
       </c>
       <c r="D819">
-        <v>45.60333729090227</v>
+        <v>55.53225712257375</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -14372,7 +14372,7 @@
         <v>822</v>
       </c>
       <c r="D820">
-        <v>46.0622610750442</v>
+        <v>55.1710781636664</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -14386,7 +14386,7 @@
         <v>823</v>
       </c>
       <c r="D821">
-        <v>46.52118485918614</v>
+        <v>54.59128132978131</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -14400,7 +14400,7 @@
         <v>824</v>
       </c>
       <c r="D822">
-        <v>46.98010864332807</v>
+        <v>50.76911314141653</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -14414,7 +14414,7 @@
         <v>825</v>
       </c>
       <c r="D823">
-        <v>47.43903242747</v>
+        <v>45.30115145136081</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -14428,7 +14428,7 @@
         <v>826</v>
       </c>
       <c r="D824">
-        <v>47.89795621161193</v>
+        <v>38.79716532615989</v>
       </c>
     </row>
     <row r="825" spans="1:4">
@@ -14442,7 +14442,7 @@
         <v>827</v>
       </c>
       <c r="D825">
-        <v>48.35687999575387</v>
+        <v>32.73673971861474</v>
       </c>
     </row>
     <row r="826" spans="1:4">
@@ -14456,7 +14456,7 @@
         <v>828</v>
       </c>
       <c r="D826">
-        <v>48.8158037798958</v>
+        <v>27.5380258863943</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -14470,7 +14470,7 @@
         <v>829</v>
       </c>
       <c r="D827">
-        <v>49.27472756403773</v>
+        <v>22.23751373218285</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -14484,7 +14484,7 @@
         <v>830</v>
       </c>
       <c r="D828">
-        <v>49.73365134817966</v>
+        <v>18.89257931108279</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -14498,7 +14498,7 @@
         <v>831</v>
       </c>
       <c r="D829">
-        <v>50.1925751323216</v>
+        <v>14.67726116105257</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -14512,7 +14512,7 @@
         <v>832</v>
       </c>
       <c r="D830">
-        <v>50.65149891646354</v>
+        <v>11.80931891100816</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -14526,7 +14526,7 @@
         <v>833</v>
       </c>
       <c r="D831">
-        <v>51.11042270060547</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -14540,7 +14540,7 @@
         <v>834</v>
       </c>
       <c r="D832">
-        <v>51.5693464847474</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="833" spans="1:4">
@@ -14554,7 +14554,7 @@
         <v>835</v>
       </c>
       <c r="D833">
-        <v>52.02827026888934</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="834" spans="1:4">
@@ -14568,7 +14568,7 @@
         <v>836</v>
       </c>
       <c r="D834">
-        <v>52.48719405303127</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -14582,7 +14582,7 @@
         <v>837</v>
       </c>
       <c r="D835">
-        <v>52.9461178371732</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -14596,7 +14596,7 @@
         <v>838</v>
       </c>
       <c r="D836">
-        <v>53.40504162131514</v>
+        <v>10.15805966694125</v>
       </c>
     </row>
   </sheetData>

--- a/spreadsheet/Grass_data_weekly_2009-2024.xlsx
+++ b/spreadsheet/Grass_data_weekly_2009-2024.xlsx
@@ -2920,7 +2920,7 @@
         <v>4</v>
       </c>
       <c r="D2">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2934,7 +2934,7 @@
         <v>5</v>
       </c>
       <c r="D3">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2948,7 +2948,7 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2962,7 +2962,7 @@
         <v>7</v>
       </c>
       <c r="D5">
-        <v>6.854528968943185</v>
+        <v>6.930118585791575</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2976,7 +2976,7 @@
         <v>8</v>
       </c>
       <c r="D6">
-        <v>7.03368572754606</v>
+        <v>6.978745030230113</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2990,7 +2990,7 @@
         <v>9</v>
       </c>
       <c r="D7">
-        <v>7.518983528026097</v>
+        <v>7.461574481879046</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3004,7 +3004,7 @@
         <v>10</v>
       </c>
       <c r="D8">
-        <v>8.425623627772788</v>
+        <v>8.389812718975181</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -3018,7 +3018,7 @@
         <v>11</v>
       </c>
       <c r="D9">
-        <v>9.526346614371672</v>
+        <v>9.689084009284043</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -3032,7 +3032,7 @@
         <v>12</v>
       </c>
       <c r="D10">
-        <v>9.975172679529194</v>
+        <v>9.897648956975232</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -3046,7 +3046,7 @@
         <v>13</v>
       </c>
       <c r="D11">
-        <v>11.18521807835811</v>
+        <v>11.29733187705322</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -3060,7 +3060,7 @@
         <v>14</v>
       </c>
       <c r="D12">
-        <v>14.22902793459837</v>
+        <v>14.15078438443025</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -3074,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="D13">
-        <v>17.3452111256389</v>
+        <v>17.27407695560362</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -3088,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="D14">
-        <v>22.38573995940518</v>
+        <v>22.33919951553991</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -3102,7 +3102,7 @@
         <v>17</v>
       </c>
       <c r="D15">
-        <v>28.23852898690002</v>
+        <v>27.98984445195714</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -3116,7 +3116,7 @@
         <v>18</v>
       </c>
       <c r="D16">
-        <v>34.8954568648472</v>
+        <v>35.19888390237617</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -3130,7 +3130,7 @@
         <v>19</v>
       </c>
       <c r="D17">
-        <v>45.56737149155249</v>
+        <v>45.05432886144337</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -3144,7 +3144,7 @@
         <v>20</v>
       </c>
       <c r="D18">
-        <v>52.46121389833615</v>
+        <v>52.16929440240701</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -3158,7 +3158,7 @@
         <v>21</v>
       </c>
       <c r="D19">
-        <v>57.03478496451859</v>
+        <v>56.57040600912357</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -3172,7 +3172,7 @@
         <v>22</v>
       </c>
       <c r="D20">
-        <v>62.58059496111045</v>
+        <v>62.49727657554863</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -3186,7 +3186,7 @@
         <v>23</v>
       </c>
       <c r="D21">
-        <v>71.69760535869358</v>
+        <v>71.29277978162189</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -3200,7 +3200,7 @@
         <v>24</v>
       </c>
       <c r="D22">
-        <v>73.97904219335875</v>
+        <v>74.20864166144314</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -3214,7 +3214,7 @@
         <v>25</v>
       </c>
       <c r="D23">
-        <v>76.1336195197991</v>
+        <v>75.75617350133528</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -3228,7 +3228,7 @@
         <v>26</v>
       </c>
       <c r="D24">
-        <v>69.5451984688922</v>
+        <v>69.23215617774684</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -3242,7 +3242,7 @@
         <v>27</v>
       </c>
       <c r="D25">
-        <v>65.48814501434239</v>
+        <v>66.35583125096437</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -3256,7 +3256,7 @@
         <v>28</v>
       </c>
       <c r="D26">
-        <v>66.4225272500118</v>
+        <v>67.28852804058688</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -3270,7 +3270,7 @@
         <v>29</v>
       </c>
       <c r="D27">
-        <v>64.03620840335277</v>
+        <v>63.53466436362915</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -3284,7 +3284,7 @@
         <v>30</v>
       </c>
       <c r="D28">
-        <v>61.85817823188949</v>
+        <v>61.39608875837782</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -3298,7 +3298,7 @@
         <v>31</v>
       </c>
       <c r="D29">
-        <v>60.44814623697598</v>
+        <v>59.82297433277076</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -3312,7 +3312,7 @@
         <v>32</v>
       </c>
       <c r="D30">
-        <v>58.91129319455056</v>
+        <v>59.99626800731946</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -3326,7 +3326,7 @@
         <v>33</v>
       </c>
       <c r="D31">
-        <v>59.81015942309325</v>
+        <v>59.59798490639051</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -3340,7 +3340,7 @@
         <v>34</v>
       </c>
       <c r="D32">
-        <v>60.67431865726294</v>
+        <v>60.0472300893551</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -3354,7 +3354,7 @@
         <v>35</v>
       </c>
       <c r="D33">
-        <v>61.54400339993682</v>
+        <v>61.84368773323343</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -3368,7 +3368,7 @@
         <v>36</v>
       </c>
       <c r="D34">
-        <v>62.37901063599286</v>
+        <v>61.92567201670877</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -3382,7 +3382,7 @@
         <v>37</v>
       </c>
       <c r="D35">
-        <v>59.73418161014251</v>
+        <v>59.66780478916508</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -3396,7 +3396,7 @@
         <v>38</v>
       </c>
       <c r="D36">
-        <v>57.10532002513312</v>
+        <v>57.16037791688875</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -3410,7 +3410,7 @@
         <v>39</v>
       </c>
       <c r="D37">
-        <v>55.53225712257375</v>
+        <v>55.79615820617291</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -3424,7 +3424,7 @@
         <v>40</v>
       </c>
       <c r="D38">
-        <v>55.1710781636664</v>
+        <v>54.64606831322272</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -3438,7 +3438,7 @@
         <v>41</v>
       </c>
       <c r="D39">
-        <v>54.59128132978131</v>
+        <v>54.68376999536412</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -3452,7 +3452,7 @@
         <v>42</v>
       </c>
       <c r="D40">
-        <v>50.76911314141653</v>
+        <v>50.86043815906314</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -3466,7 +3466,7 @@
         <v>43</v>
       </c>
       <c r="D41">
-        <v>45.30115145136081</v>
+        <v>45.28851709401708</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -3480,7 +3480,7 @@
         <v>44</v>
       </c>
       <c r="D42">
-        <v>38.79716532615989</v>
+        <v>38.80453135834753</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -3494,7 +3494,7 @@
         <v>45</v>
       </c>
       <c r="D43">
-        <v>32.73673971861474</v>
+        <v>32.56216513878279</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -3508,7 +3508,7 @@
         <v>46</v>
       </c>
       <c r="D44">
-        <v>27.5380258863943</v>
+        <v>27.68223375970436</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -3522,7 +3522,7 @@
         <v>47</v>
       </c>
       <c r="D45">
-        <v>22.23751373218285</v>
+        <v>22.33114531198935</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -3536,7 +3536,7 @@
         <v>48</v>
       </c>
       <c r="D46">
-        <v>18.89257931108279</v>
+        <v>18.69653137750623</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -3550,7 +3550,7 @@
         <v>49</v>
       </c>
       <c r="D47">
-        <v>14.67726116105257</v>
+        <v>14.8529093132343</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -3564,7 +3564,7 @@
         <v>50</v>
       </c>
       <c r="D48">
-        <v>11.80931891100816</v>
+        <v>11.93737215295884</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -3578,7 +3578,7 @@
         <v>51</v>
       </c>
       <c r="D49">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -3592,7 +3592,7 @@
         <v>52</v>
       </c>
       <c r="D50">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -3606,7 +3606,7 @@
         <v>53</v>
       </c>
       <c r="D51">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -3620,7 +3620,7 @@
         <v>54</v>
       </c>
       <c r="D52">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -3634,7 +3634,7 @@
         <v>55</v>
       </c>
       <c r="D53">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -3648,7 +3648,7 @@
         <v>56</v>
       </c>
       <c r="D54">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -3662,7 +3662,7 @@
         <v>57</v>
       </c>
       <c r="D55">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -3676,7 +3676,7 @@
         <v>58</v>
       </c>
       <c r="D56">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -3690,7 +3690,7 @@
         <v>59</v>
       </c>
       <c r="D57">
-        <v>6.854528968943185</v>
+        <v>6.930118585791575</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -3704,7 +3704,7 @@
         <v>60</v>
       </c>
       <c r="D58">
-        <v>7.03368572754606</v>
+        <v>6.978745030230113</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -3718,7 +3718,7 @@
         <v>61</v>
       </c>
       <c r="D59">
-        <v>7.518983528026097</v>
+        <v>7.461574481879046</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -3732,7 +3732,7 @@
         <v>62</v>
       </c>
       <c r="D60">
-        <v>8.425623627772788</v>
+        <v>8.389812718975181</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -3746,7 +3746,7 @@
         <v>63</v>
       </c>
       <c r="D61">
-        <v>9.526346614371672</v>
+        <v>9.689084009284043</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -3760,7 +3760,7 @@
         <v>64</v>
       </c>
       <c r="D62">
-        <v>9.975172679529194</v>
+        <v>9.897648956975232</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -3774,7 +3774,7 @@
         <v>65</v>
       </c>
       <c r="D63">
-        <v>11.18521807835811</v>
+        <v>11.29733187705322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -3788,7 +3788,7 @@
         <v>66</v>
       </c>
       <c r="D64">
-        <v>14.22902793459837</v>
+        <v>14.15078438443025</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -3802,7 +3802,7 @@
         <v>67</v>
       </c>
       <c r="D65">
-        <v>17.3452111256389</v>
+        <v>17.27407695560362</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -3816,7 +3816,7 @@
         <v>68</v>
       </c>
       <c r="D66">
-        <v>22.38573995940518</v>
+        <v>22.33919951553991</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -3830,7 +3830,7 @@
         <v>69</v>
       </c>
       <c r="D67">
-        <v>28.23852898690002</v>
+        <v>27.98984445195714</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -3844,7 +3844,7 @@
         <v>70</v>
       </c>
       <c r="D68">
-        <v>34.8954568648472</v>
+        <v>35.19888390237617</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -3858,7 +3858,7 @@
         <v>71</v>
       </c>
       <c r="D69">
-        <v>45.56737149155249</v>
+        <v>45.05432886144337</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -3872,7 +3872,7 @@
         <v>72</v>
       </c>
       <c r="D70">
-        <v>52.46121389833615</v>
+        <v>52.16929440240701</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -3886,7 +3886,7 @@
         <v>73</v>
       </c>
       <c r="D71">
-        <v>57.03478496451859</v>
+        <v>56.57040600912357</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -3900,7 +3900,7 @@
         <v>74</v>
       </c>
       <c r="D72">
-        <v>62.58059496111045</v>
+        <v>62.49727657554863</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -3914,7 +3914,7 @@
         <v>75</v>
       </c>
       <c r="D73">
-        <v>71.69760535869358</v>
+        <v>71.29277978162189</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -3928,7 +3928,7 @@
         <v>76</v>
       </c>
       <c r="D74">
-        <v>73.97904219335875</v>
+        <v>74.20864166144314</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -3942,7 +3942,7 @@
         <v>77</v>
       </c>
       <c r="D75">
-        <v>76.1336195197991</v>
+        <v>75.75617350133528</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -3956,7 +3956,7 @@
         <v>78</v>
       </c>
       <c r="D76">
-        <v>69.5451984688922</v>
+        <v>69.23215617774684</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3970,7 +3970,7 @@
         <v>79</v>
       </c>
       <c r="D77">
-        <v>65.48814501434239</v>
+        <v>66.35583125096437</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3984,7 +3984,7 @@
         <v>80</v>
       </c>
       <c r="D78">
-        <v>66.4225272500118</v>
+        <v>67.28852804058688</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3998,7 +3998,7 @@
         <v>81</v>
       </c>
       <c r="D79">
-        <v>64.03620840335277</v>
+        <v>63.53466436362915</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -4012,7 +4012,7 @@
         <v>82</v>
       </c>
       <c r="D80">
-        <v>61.85817823188949</v>
+        <v>61.39608875837782</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -4026,7 +4026,7 @@
         <v>83</v>
       </c>
       <c r="D81">
-        <v>60.44814623697598</v>
+        <v>59.82297433277076</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -4040,7 +4040,7 @@
         <v>84</v>
       </c>
       <c r="D82">
-        <v>58.91129319455056</v>
+        <v>59.99626800731946</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -4054,7 +4054,7 @@
         <v>85</v>
       </c>
       <c r="D83">
-        <v>59.81015942309325</v>
+        <v>59.59798490639051</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -4068,7 +4068,7 @@
         <v>86</v>
       </c>
       <c r="D84">
-        <v>60.67431865726294</v>
+        <v>60.0472300893551</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -4082,7 +4082,7 @@
         <v>87</v>
       </c>
       <c r="D85">
-        <v>61.54400339993682</v>
+        <v>61.84368773323343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -4096,7 +4096,7 @@
         <v>88</v>
       </c>
       <c r="D86">
-        <v>62.37901063599286</v>
+        <v>61.92567201670877</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -4110,7 +4110,7 @@
         <v>89</v>
       </c>
       <c r="D87">
-        <v>59.73418161014251</v>
+        <v>59.66780478916508</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -4124,7 +4124,7 @@
         <v>90</v>
       </c>
       <c r="D88">
-        <v>57.10532002513312</v>
+        <v>57.16037791688875</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -4138,7 +4138,7 @@
         <v>91</v>
       </c>
       <c r="D89">
-        <v>55.53225712257375</v>
+        <v>55.79615820617291</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -4152,7 +4152,7 @@
         <v>92</v>
       </c>
       <c r="D90">
-        <v>55.1710781636664</v>
+        <v>54.64606831322272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -4166,7 +4166,7 @@
         <v>93</v>
       </c>
       <c r="D91">
-        <v>54.59128132978131</v>
+        <v>54.68376999536412</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -4180,7 +4180,7 @@
         <v>94</v>
       </c>
       <c r="D92">
-        <v>50.76911314141653</v>
+        <v>50.86043815906314</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -4194,7 +4194,7 @@
         <v>95</v>
       </c>
       <c r="D93">
-        <v>45.30115145136081</v>
+        <v>45.28851709401708</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -4208,7 +4208,7 @@
         <v>96</v>
       </c>
       <c r="D94">
-        <v>38.79716532615989</v>
+        <v>38.80453135834753</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -4222,7 +4222,7 @@
         <v>97</v>
       </c>
       <c r="D95">
-        <v>32.73673971861474</v>
+        <v>32.56216513878279</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -4236,7 +4236,7 @@
         <v>98</v>
       </c>
       <c r="D96">
-        <v>27.5380258863943</v>
+        <v>27.68223375970436</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -4250,7 +4250,7 @@
         <v>99</v>
       </c>
       <c r="D97">
-        <v>22.23751373218285</v>
+        <v>22.33114531198935</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -4264,7 +4264,7 @@
         <v>100</v>
       </c>
       <c r="D98">
-        <v>18.89257931108279</v>
+        <v>18.69653137750623</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -4278,7 +4278,7 @@
         <v>101</v>
       </c>
       <c r="D99">
-        <v>14.67726116105257</v>
+        <v>14.8529093132343</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -4292,7 +4292,7 @@
         <v>102</v>
       </c>
       <c r="D100">
-        <v>11.80931891100816</v>
+        <v>11.93737215295884</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -4306,7 +4306,7 @@
         <v>103</v>
       </c>
       <c r="D101">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -4320,7 +4320,7 @@
         <v>104</v>
       </c>
       <c r="D102">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -4334,7 +4334,7 @@
         <v>105</v>
       </c>
       <c r="D103">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -4348,7 +4348,7 @@
         <v>106</v>
       </c>
       <c r="D104">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -4362,7 +4362,7 @@
         <v>107</v>
       </c>
       <c r="D105">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -4376,7 +4376,7 @@
         <v>108</v>
       </c>
       <c r="D106">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -4390,7 +4390,7 @@
         <v>109</v>
       </c>
       <c r="D107">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -4404,7 +4404,7 @@
         <v>110</v>
       </c>
       <c r="D108">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -4418,7 +4418,7 @@
         <v>111</v>
       </c>
       <c r="D109">
-        <v>6.854528968943185</v>
+        <v>6.930118585791575</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -4432,7 +4432,7 @@
         <v>112</v>
       </c>
       <c r="D110">
-        <v>7.03368572754606</v>
+        <v>6.978745030230113</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -4446,7 +4446,7 @@
         <v>113</v>
       </c>
       <c r="D111">
-        <v>7.518983528026097</v>
+        <v>7.461574481879046</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -4460,7 +4460,7 @@
         <v>114</v>
       </c>
       <c r="D112">
-        <v>8.425623627772788</v>
+        <v>8.389812718975181</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -4474,7 +4474,7 @@
         <v>115</v>
       </c>
       <c r="D113">
-        <v>9.526346614371672</v>
+        <v>9.689084009284043</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -4488,7 +4488,7 @@
         <v>116</v>
       </c>
       <c r="D114">
-        <v>9.975172679529194</v>
+        <v>9.897648956975232</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -4502,7 +4502,7 @@
         <v>117</v>
       </c>
       <c r="D115">
-        <v>11.18521807835811</v>
+        <v>11.29733187705322</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -4516,7 +4516,7 @@
         <v>118</v>
       </c>
       <c r="D116">
-        <v>14.22902793459837</v>
+        <v>14.15078438443025</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -4530,7 +4530,7 @@
         <v>119</v>
       </c>
       <c r="D117">
-        <v>17.3452111256389</v>
+        <v>17.27407695560362</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -4544,7 +4544,7 @@
         <v>120</v>
       </c>
       <c r="D118">
-        <v>22.38573995940518</v>
+        <v>22.33919951553991</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -4558,7 +4558,7 @@
         <v>121</v>
       </c>
       <c r="D119">
-        <v>28.23852898690002</v>
+        <v>27.98984445195714</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -4572,7 +4572,7 @@
         <v>122</v>
       </c>
       <c r="D120">
-        <v>34.8954568648472</v>
+        <v>35.19888390237617</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -4586,7 +4586,7 @@
         <v>123</v>
       </c>
       <c r="D121">
-        <v>45.56737149155249</v>
+        <v>45.05432886144337</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -4600,7 +4600,7 @@
         <v>124</v>
       </c>
       <c r="D122">
-        <v>52.46121389833615</v>
+        <v>52.16929440240701</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -4614,7 +4614,7 @@
         <v>125</v>
       </c>
       <c r="D123">
-        <v>57.03478496451859</v>
+        <v>56.57040600912357</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -4628,7 +4628,7 @@
         <v>126</v>
       </c>
       <c r="D124">
-        <v>62.58059496111045</v>
+        <v>62.49727657554863</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -4642,7 +4642,7 @@
         <v>127</v>
       </c>
       <c r="D125">
-        <v>71.69760535869358</v>
+        <v>71.29277978162189</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -4656,7 +4656,7 @@
         <v>128</v>
       </c>
       <c r="D126">
-        <v>73.97904219335875</v>
+        <v>74.20864166144314</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -4670,7 +4670,7 @@
         <v>129</v>
       </c>
       <c r="D127">
-        <v>76.1336195197991</v>
+        <v>75.75617350133528</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -4684,7 +4684,7 @@
         <v>130</v>
       </c>
       <c r="D128">
-        <v>69.5451984688922</v>
+        <v>69.23215617774684</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -4698,7 +4698,7 @@
         <v>131</v>
       </c>
       <c r="D129">
-        <v>65.48814501434239</v>
+        <v>66.35583125096437</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -4712,7 +4712,7 @@
         <v>132</v>
       </c>
       <c r="D130">
-        <v>66.4225272500118</v>
+        <v>67.28852804058688</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -4726,7 +4726,7 @@
         <v>133</v>
       </c>
       <c r="D131">
-        <v>64.03620840335277</v>
+        <v>63.53466436362915</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -4740,7 +4740,7 @@
         <v>134</v>
       </c>
       <c r="D132">
-        <v>61.85817823188949</v>
+        <v>61.39608875837782</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -4754,7 +4754,7 @@
         <v>135</v>
       </c>
       <c r="D133">
-        <v>60.44814623697598</v>
+        <v>59.82297433277076</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -4768,7 +4768,7 @@
         <v>136</v>
       </c>
       <c r="D134">
-        <v>58.91129319455056</v>
+        <v>59.99626800731946</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -4782,7 +4782,7 @@
         <v>137</v>
       </c>
       <c r="D135">
-        <v>59.81015942309325</v>
+        <v>59.59798490639051</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -4796,7 +4796,7 @@
         <v>138</v>
       </c>
       <c r="D136">
-        <v>60.67431865726294</v>
+        <v>60.0472300893551</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -4810,7 +4810,7 @@
         <v>139</v>
       </c>
       <c r="D137">
-        <v>61.54400339993682</v>
+        <v>61.84368773323343</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -4824,7 +4824,7 @@
         <v>140</v>
       </c>
       <c r="D138">
-        <v>62.37901063599286</v>
+        <v>61.92567201670877</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -4838,7 +4838,7 @@
         <v>141</v>
       </c>
       <c r="D139">
-        <v>59.73418161014251</v>
+        <v>59.66780478916508</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -4852,7 +4852,7 @@
         <v>142</v>
       </c>
       <c r="D140">
-        <v>57.10532002513312</v>
+        <v>57.16037791688875</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -4866,7 +4866,7 @@
         <v>143</v>
       </c>
       <c r="D141">
-        <v>55.53225712257375</v>
+        <v>55.79615820617291</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -4880,7 +4880,7 @@
         <v>144</v>
       </c>
       <c r="D142">
-        <v>55.1710781636664</v>
+        <v>54.64606831322272</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -4894,7 +4894,7 @@
         <v>145</v>
       </c>
       <c r="D143">
-        <v>54.59128132978131</v>
+        <v>54.68376999536412</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -4908,7 +4908,7 @@
         <v>146</v>
       </c>
       <c r="D144">
-        <v>50.76911314141653</v>
+        <v>50.86043815906314</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -4922,7 +4922,7 @@
         <v>147</v>
       </c>
       <c r="D145">
-        <v>45.30115145136081</v>
+        <v>45.28851709401708</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -4936,7 +4936,7 @@
         <v>148</v>
       </c>
       <c r="D146">
-        <v>38.79716532615989</v>
+        <v>38.80453135834753</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -4950,7 +4950,7 @@
         <v>149</v>
       </c>
       <c r="D147">
-        <v>32.73673971861474</v>
+        <v>32.56216513878279</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4964,7 +4964,7 @@
         <v>150</v>
       </c>
       <c r="D148">
-        <v>27.5380258863943</v>
+        <v>27.68223375970436</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4978,7 +4978,7 @@
         <v>151</v>
       </c>
       <c r="D149">
-        <v>22.23751373218285</v>
+        <v>22.33114531198935</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4992,7 +4992,7 @@
         <v>152</v>
       </c>
       <c r="D150">
-        <v>18.89257931108279</v>
+        <v>18.69653137750623</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -5006,7 +5006,7 @@
         <v>153</v>
       </c>
       <c r="D151">
-        <v>14.67726116105257</v>
+        <v>14.8529093132343</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -5020,7 +5020,7 @@
         <v>154</v>
       </c>
       <c r="D152">
-        <v>11.80931891100816</v>
+        <v>11.93737215295884</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -5034,7 +5034,7 @@
         <v>155</v>
       </c>
       <c r="D153">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -5048,7 +5048,7 @@
         <v>156</v>
       </c>
       <c r="D154">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -5062,7 +5062,7 @@
         <v>157</v>
       </c>
       <c r="D155">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -5076,7 +5076,7 @@
         <v>158</v>
       </c>
       <c r="D156">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -5090,7 +5090,7 @@
         <v>159</v>
       </c>
       <c r="D157">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -5104,7 +5104,7 @@
         <v>160</v>
       </c>
       <c r="D158">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -5118,7 +5118,7 @@
         <v>161</v>
       </c>
       <c r="D159">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -5132,7 +5132,7 @@
         <v>162</v>
       </c>
       <c r="D160">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -5146,7 +5146,7 @@
         <v>163</v>
       </c>
       <c r="D161">
-        <v>6.854528968943185</v>
+        <v>6.930118585791575</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -5160,7 +5160,7 @@
         <v>164</v>
       </c>
       <c r="D162">
-        <v>7.03368572754606</v>
+        <v>6.978745030230113</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -5174,7 +5174,7 @@
         <v>165</v>
       </c>
       <c r="D163">
-        <v>7.518983528026097</v>
+        <v>7.461574481879046</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -5188,7 +5188,7 @@
         <v>166</v>
       </c>
       <c r="D164">
-        <v>8.425623627772788</v>
+        <v>8.389812718975181</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -5202,7 +5202,7 @@
         <v>167</v>
       </c>
       <c r="D165">
-        <v>9.526346614371672</v>
+        <v>9.689084009284043</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -5216,7 +5216,7 @@
         <v>168</v>
       </c>
       <c r="D166">
-        <v>9.975172679529194</v>
+        <v>9.897648956975232</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -5230,7 +5230,7 @@
         <v>169</v>
       </c>
       <c r="D167">
-        <v>11.18521807835811</v>
+        <v>11.29733187705322</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -5244,7 +5244,7 @@
         <v>170</v>
       </c>
       <c r="D168">
-        <v>14.22902793459837</v>
+        <v>14.15078438443025</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -5258,7 +5258,7 @@
         <v>171</v>
       </c>
       <c r="D169">
-        <v>17.3452111256389</v>
+        <v>17.27407695560362</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -5272,7 +5272,7 @@
         <v>172</v>
       </c>
       <c r="D170">
-        <v>22.38573995940518</v>
+        <v>22.33919951553991</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -5286,7 +5286,7 @@
         <v>173</v>
       </c>
       <c r="D171">
-        <v>28.23852898690002</v>
+        <v>27.98984445195714</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -5300,7 +5300,7 @@
         <v>174</v>
       </c>
       <c r="D172">
-        <v>34.8954568648472</v>
+        <v>35.19888390237617</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -5314,7 +5314,7 @@
         <v>175</v>
       </c>
       <c r="D173">
-        <v>45.56737149155249</v>
+        <v>45.05432886144337</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -5328,7 +5328,7 @@
         <v>176</v>
       </c>
       <c r="D174">
-        <v>52.46121389833615</v>
+        <v>52.16929440240701</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -5342,7 +5342,7 @@
         <v>177</v>
       </c>
       <c r="D175">
-        <v>57.03478496451859</v>
+        <v>56.57040600912357</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -5356,7 +5356,7 @@
         <v>178</v>
       </c>
       <c r="D176">
-        <v>62.58059496111045</v>
+        <v>62.49727657554863</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -5370,7 +5370,7 @@
         <v>179</v>
       </c>
       <c r="D177">
-        <v>71.69760535869358</v>
+        <v>71.29277978162189</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -5384,7 +5384,7 @@
         <v>180</v>
       </c>
       <c r="D178">
-        <v>73.97904219335875</v>
+        <v>74.20864166144314</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -5398,7 +5398,7 @@
         <v>181</v>
       </c>
       <c r="D179">
-        <v>76.1336195197991</v>
+        <v>75.75617350133528</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -5412,7 +5412,7 @@
         <v>182</v>
       </c>
       <c r="D180">
-        <v>69.5451984688922</v>
+        <v>69.23215617774684</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -5426,7 +5426,7 @@
         <v>183</v>
       </c>
       <c r="D181">
-        <v>65.48814501434239</v>
+        <v>66.35583125096437</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -5440,7 +5440,7 @@
         <v>184</v>
       </c>
       <c r="D182">
-        <v>66.4225272500118</v>
+        <v>67.28852804058688</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -5454,7 +5454,7 @@
         <v>185</v>
       </c>
       <c r="D183">
-        <v>64.03620840335277</v>
+        <v>63.53466436362915</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -5468,7 +5468,7 @@
         <v>186</v>
       </c>
       <c r="D184">
-        <v>61.85817823188949</v>
+        <v>61.39608875837782</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -5482,7 +5482,7 @@
         <v>187</v>
       </c>
       <c r="D185">
-        <v>60.44814623697598</v>
+        <v>59.82297433277076</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -5496,7 +5496,7 @@
         <v>188</v>
       </c>
       <c r="D186">
-        <v>58.91129319455056</v>
+        <v>59.99626800731946</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -5510,7 +5510,7 @@
         <v>189</v>
       </c>
       <c r="D187">
-        <v>59.81015942309325</v>
+        <v>59.59798490639051</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -5524,7 +5524,7 @@
         <v>190</v>
       </c>
       <c r="D188">
-        <v>60.67431865726294</v>
+        <v>60.0472300893551</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -5538,7 +5538,7 @@
         <v>191</v>
       </c>
       <c r="D189">
-        <v>61.54400339993682</v>
+        <v>61.84368773323343</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -5552,7 +5552,7 @@
         <v>192</v>
       </c>
       <c r="D190">
-        <v>62.37901063599286</v>
+        <v>61.92567201670877</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -5566,7 +5566,7 @@
         <v>193</v>
       </c>
       <c r="D191">
-        <v>59.73418161014251</v>
+        <v>59.66780478916508</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -5580,7 +5580,7 @@
         <v>194</v>
       </c>
       <c r="D192">
-        <v>57.10532002513312</v>
+        <v>57.16037791688875</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -5594,7 +5594,7 @@
         <v>195</v>
       </c>
       <c r="D193">
-        <v>55.53225712257375</v>
+        <v>55.79615820617291</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -5608,7 +5608,7 @@
         <v>196</v>
       </c>
       <c r="D194">
-        <v>55.1710781636664</v>
+        <v>54.64606831322272</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -5622,7 +5622,7 @@
         <v>197</v>
       </c>
       <c r="D195">
-        <v>54.59128132978131</v>
+        <v>54.68376999536412</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -5636,7 +5636,7 @@
         <v>198</v>
       </c>
       <c r="D196">
-        <v>50.76911314141653</v>
+        <v>50.86043815906314</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -5650,7 +5650,7 @@
         <v>199</v>
       </c>
       <c r="D197">
-        <v>45.30115145136081</v>
+        <v>45.28851709401708</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -5664,7 +5664,7 @@
         <v>200</v>
       </c>
       <c r="D198">
-        <v>38.79716532615989</v>
+        <v>38.80453135834753</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -5678,7 +5678,7 @@
         <v>201</v>
       </c>
       <c r="D199">
-        <v>32.73673971861474</v>
+        <v>32.56216513878279</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -5692,7 +5692,7 @@
         <v>202</v>
       </c>
       <c r="D200">
-        <v>27.5380258863943</v>
+        <v>27.68223375970436</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -5706,7 +5706,7 @@
         <v>203</v>
       </c>
       <c r="D201">
-        <v>22.23751373218285</v>
+        <v>22.33114531198935</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -5720,7 +5720,7 @@
         <v>204</v>
       </c>
       <c r="D202">
-        <v>18.89257931108279</v>
+        <v>18.69653137750623</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -5734,7 +5734,7 @@
         <v>205</v>
       </c>
       <c r="D203">
-        <v>14.67726116105257</v>
+        <v>14.8529093132343</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -5748,7 +5748,7 @@
         <v>206</v>
       </c>
       <c r="D204">
-        <v>11.80931891100816</v>
+        <v>11.93737215295884</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -5762,7 +5762,7 @@
         <v>207</v>
       </c>
       <c r="D205">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -5776,7 +5776,7 @@
         <v>208</v>
       </c>
       <c r="D206">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -5790,7 +5790,7 @@
         <v>209</v>
       </c>
       <c r="D207">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -5804,7 +5804,7 @@
         <v>210</v>
       </c>
       <c r="D208">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -5818,7 +5818,7 @@
         <v>211</v>
       </c>
       <c r="D209">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -5832,7 +5832,7 @@
         <v>212</v>
       </c>
       <c r="D210">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -5846,7 +5846,7 @@
         <v>213</v>
       </c>
       <c r="D211">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -5860,7 +5860,7 @@
         <v>214</v>
       </c>
       <c r="D212">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -6504,7 +6504,7 @@
         <v>260</v>
       </c>
       <c r="D258">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -6518,7 +6518,7 @@
         <v>261</v>
       </c>
       <c r="D259">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -6532,7 +6532,7 @@
         <v>262</v>
       </c>
       <c r="D260">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -6546,7 +6546,7 @@
         <v>263</v>
       </c>
       <c r="D261">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -6560,7 +6560,7 @@
         <v>264</v>
       </c>
       <c r="D262">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -6574,7 +6574,7 @@
         <v>265</v>
       </c>
       <c r="D263">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -6588,7 +6588,7 @@
         <v>266</v>
       </c>
       <c r="D264">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -6602,7 +6602,7 @@
         <v>267</v>
       </c>
       <c r="D265">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -7246,7 +7246,7 @@
         <v>313</v>
       </c>
       <c r="D311">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -7260,7 +7260,7 @@
         <v>314</v>
       </c>
       <c r="D312">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -7274,7 +7274,7 @@
         <v>315</v>
       </c>
       <c r="D313">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -7288,7 +7288,7 @@
         <v>316</v>
       </c>
       <c r="D314">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -7302,7 +7302,7 @@
         <v>317</v>
       </c>
       <c r="D315">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -7316,7 +7316,7 @@
         <v>318</v>
       </c>
       <c r="D316">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -7330,7 +7330,7 @@
         <v>319</v>
       </c>
       <c r="D317">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -7974,7 +7974,7 @@
         <v>365</v>
       </c>
       <c r="D363">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -7988,7 +7988,7 @@
         <v>366</v>
       </c>
       <c r="D364">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -8002,7 +8002,7 @@
         <v>367</v>
       </c>
       <c r="D365">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -8016,7 +8016,7 @@
         <v>368</v>
       </c>
       <c r="D366">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -8030,7 +8030,7 @@
         <v>369</v>
       </c>
       <c r="D367">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -8044,7 +8044,7 @@
         <v>370</v>
       </c>
       <c r="D368">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -8058,7 +8058,7 @@
         <v>371</v>
       </c>
       <c r="D369">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="370" spans="1:4">
@@ -8702,7 +8702,7 @@
         <v>417</v>
       </c>
       <c r="D415">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="416" spans="1:4">
@@ -8716,7 +8716,7 @@
         <v>418</v>
       </c>
       <c r="D416">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="417" spans="1:4">
@@ -8730,7 +8730,7 @@
         <v>419</v>
       </c>
       <c r="D417">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="418" spans="1:4">
@@ -8744,7 +8744,7 @@
         <v>420</v>
       </c>
       <c r="D418">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="419" spans="1:4">
@@ -8758,7 +8758,7 @@
         <v>421</v>
       </c>
       <c r="D419">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="420" spans="1:4">
@@ -8772,7 +8772,7 @@
         <v>422</v>
       </c>
       <c r="D420">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="421" spans="1:4">
@@ -8786,7 +8786,7 @@
         <v>423</v>
       </c>
       <c r="D421">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="422" spans="1:4">
@@ -9430,7 +9430,7 @@
         <v>469</v>
       </c>
       <c r="D467">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="468" spans="1:4">
@@ -9444,7 +9444,7 @@
         <v>470</v>
       </c>
       <c r="D468">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="469" spans="1:4">
@@ -9458,7 +9458,7 @@
         <v>471</v>
       </c>
       <c r="D469">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="470" spans="1:4">
@@ -9472,7 +9472,7 @@
         <v>472</v>
       </c>
       <c r="D470">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="471" spans="1:4">
@@ -9486,7 +9486,7 @@
         <v>473</v>
       </c>
       <c r="D471">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="472" spans="1:4">
@@ -9500,7 +9500,7 @@
         <v>474</v>
       </c>
       <c r="D472">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="473" spans="1:4">
@@ -9514,7 +9514,7 @@
         <v>475</v>
       </c>
       <c r="D473">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="474" spans="1:4">
@@ -10158,7 +10158,7 @@
         <v>521</v>
       </c>
       <c r="D519">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="520" spans="1:4">
@@ -10172,7 +10172,7 @@
         <v>522</v>
       </c>
       <c r="D520">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="521" spans="1:4">
@@ -10186,7 +10186,7 @@
         <v>523</v>
       </c>
       <c r="D521">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="522" spans="1:4">
@@ -10200,7 +10200,7 @@
         <v>524</v>
       </c>
       <c r="D522">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="523" spans="1:4">
@@ -10214,7 +10214,7 @@
         <v>525</v>
       </c>
       <c r="D523">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="524" spans="1:4">
@@ -10228,7 +10228,7 @@
         <v>526</v>
       </c>
       <c r="D524">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="525" spans="1:4">
@@ -10242,7 +10242,7 @@
         <v>527</v>
       </c>
       <c r="D525">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="526" spans="1:4">
@@ -10886,7 +10886,7 @@
         <v>573</v>
       </c>
       <c r="D571">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="572" spans="1:4">
@@ -10900,7 +10900,7 @@
         <v>574</v>
       </c>
       <c r="D572">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="573" spans="1:4">
@@ -10914,7 +10914,7 @@
         <v>575</v>
       </c>
       <c r="D573">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="574" spans="1:4">
@@ -10928,7 +10928,7 @@
         <v>576</v>
       </c>
       <c r="D574">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="575" spans="1:4">
@@ -10942,7 +10942,7 @@
         <v>577</v>
       </c>
       <c r="D575">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="576" spans="1:4">
@@ -10956,7 +10956,7 @@
         <v>578</v>
       </c>
       <c r="D576">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="577" spans="1:4">
@@ -10970,7 +10970,7 @@
         <v>579</v>
       </c>
       <c r="D577">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="578" spans="1:4">
@@ -10984,7 +10984,7 @@
         <v>580</v>
       </c>
       <c r="D578">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="579" spans="1:4">
@@ -11628,7 +11628,7 @@
         <v>626</v>
       </c>
       <c r="D624">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="625" spans="1:4">
@@ -11642,7 +11642,7 @@
         <v>627</v>
       </c>
       <c r="D625">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="626" spans="1:4">
@@ -11656,7 +11656,7 @@
         <v>628</v>
       </c>
       <c r="D626">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="627" spans="1:4">
@@ -11670,7 +11670,7 @@
         <v>629</v>
       </c>
       <c r="D627">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="628" spans="1:4">
@@ -11684,7 +11684,7 @@
         <v>630</v>
       </c>
       <c r="D628">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="629" spans="1:4">
@@ -11698,7 +11698,7 @@
         <v>631</v>
       </c>
       <c r="D629">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="630" spans="1:4">
@@ -11712,7 +11712,7 @@
         <v>632</v>
       </c>
       <c r="D630">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="631" spans="1:4">
@@ -12356,7 +12356,7 @@
         <v>678</v>
       </c>
       <c r="D676">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="677" spans="1:4">
@@ -12370,7 +12370,7 @@
         <v>679</v>
       </c>
       <c r="D677">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="678" spans="1:4">
@@ -12384,7 +12384,7 @@
         <v>680</v>
       </c>
       <c r="D678">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="679" spans="1:4">
@@ -12398,7 +12398,7 @@
         <v>681</v>
       </c>
       <c r="D679">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="680" spans="1:4">
@@ -12412,7 +12412,7 @@
         <v>682</v>
       </c>
       <c r="D680">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="681" spans="1:4">
@@ -12426,7 +12426,7 @@
         <v>683</v>
       </c>
       <c r="D681">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="682" spans="1:4">
@@ -12440,7 +12440,7 @@
         <v>684</v>
       </c>
       <c r="D682">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="683" spans="1:4">
@@ -13084,7 +13084,7 @@
         <v>730</v>
       </c>
       <c r="D728">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="729" spans="1:4">
@@ -13098,7 +13098,7 @@
         <v>731</v>
       </c>
       <c r="D729">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="730" spans="1:4">
@@ -13112,7 +13112,7 @@
         <v>732</v>
       </c>
       <c r="D730">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="731" spans="1:4">
@@ -13126,7 +13126,7 @@
         <v>733</v>
       </c>
       <c r="D731">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="732" spans="1:4">
@@ -13140,7 +13140,7 @@
         <v>734</v>
       </c>
       <c r="D732">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="733" spans="1:4">
@@ -13154,7 +13154,7 @@
         <v>735</v>
       </c>
       <c r="D733">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="734" spans="1:4">
@@ -13168,7 +13168,7 @@
         <v>736</v>
       </c>
       <c r="D734">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="735" spans="1:4">
@@ -13812,7 +13812,7 @@
         <v>782</v>
       </c>
       <c r="D780">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="781" spans="1:4">
@@ -13826,7 +13826,7 @@
         <v>783</v>
       </c>
       <c r="D781">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="782" spans="1:4">
@@ -13840,7 +13840,7 @@
         <v>784</v>
       </c>
       <c r="D782">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="783" spans="1:4">
@@ -13854,7 +13854,7 @@
         <v>785</v>
       </c>
       <c r="D783">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="784" spans="1:4">
@@ -13868,7 +13868,7 @@
         <v>786</v>
       </c>
       <c r="D784">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="785" spans="1:4">
@@ -13882,7 +13882,7 @@
         <v>787</v>
       </c>
       <c r="D785">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="786" spans="1:4">
@@ -13896,7 +13896,7 @@
         <v>788</v>
       </c>
       <c r="D786">
-        <v>8.646967651357356</v>
+        <v>8.79280488955489</v>
       </c>
     </row>
     <row r="787" spans="1:4">
@@ -14106,7 +14106,7 @@
         <v>803</v>
       </c>
       <c r="D801">
-        <v>57.03478496451859</v>
+        <v>56.57040600912357</v>
       </c>
     </row>
     <row r="802" spans="1:4">
@@ -14120,7 +14120,7 @@
         <v>804</v>
       </c>
       <c r="D802">
-        <v>62.58059496111045</v>
+        <v>62.49727657554863</v>
       </c>
     </row>
     <row r="803" spans="1:4">
@@ -14134,7 +14134,7 @@
         <v>805</v>
       </c>
       <c r="D803">
-        <v>71.69760535869358</v>
+        <v>71.29277978162189</v>
       </c>
     </row>
     <row r="804" spans="1:4">
@@ -14148,7 +14148,7 @@
         <v>806</v>
       </c>
       <c r="D804">
-        <v>73.97904219335875</v>
+        <v>74.20864166144314</v>
       </c>
     </row>
     <row r="805" spans="1:4">
@@ -14162,7 +14162,7 @@
         <v>807</v>
       </c>
       <c r="D805">
-        <v>76.1336195197991</v>
+        <v>75.75617350133528</v>
       </c>
     </row>
     <row r="806" spans="1:4">
@@ -14176,7 +14176,7 @@
         <v>808</v>
       </c>
       <c r="D806">
-        <v>69.5451984688922</v>
+        <v>69.23215617774684</v>
       </c>
     </row>
     <row r="807" spans="1:4">
@@ -14190,7 +14190,7 @@
         <v>809</v>
       </c>
       <c r="D807">
-        <v>65.48814501434239</v>
+        <v>66.35583125096437</v>
       </c>
     </row>
     <row r="808" spans="1:4">
@@ -14204,7 +14204,7 @@
         <v>810</v>
       </c>
       <c r="D808">
-        <v>66.4225272500118</v>
+        <v>67.28852804058688</v>
       </c>
     </row>
     <row r="809" spans="1:4">
@@ -14218,7 +14218,7 @@
         <v>811</v>
       </c>
       <c r="D809">
-        <v>64.03620840335277</v>
+        <v>63.53466436362915</v>
       </c>
     </row>
     <row r="810" spans="1:4">
@@ -14232,7 +14232,7 @@
         <v>812</v>
       </c>
       <c r="D810">
-        <v>61.85817823188949</v>
+        <v>61.39608875837782</v>
       </c>
     </row>
     <row r="811" spans="1:4">
@@ -14246,7 +14246,7 @@
         <v>813</v>
       </c>
       <c r="D811">
-        <v>60.44814623697598</v>
+        <v>59.82297433277076</v>
       </c>
     </row>
     <row r="812" spans="1:4">
@@ -14260,7 +14260,7 @@
         <v>814</v>
       </c>
       <c r="D812">
-        <v>58.91129319455056</v>
+        <v>59.99626800731946</v>
       </c>
     </row>
     <row r="813" spans="1:4">
@@ -14274,7 +14274,7 @@
         <v>815</v>
       </c>
       <c r="D813">
-        <v>59.81015942309325</v>
+        <v>59.59798490639051</v>
       </c>
     </row>
     <row r="814" spans="1:4">
@@ -14288,7 +14288,7 @@
         <v>816</v>
       </c>
       <c r="D814">
-        <v>60.67431865726294</v>
+        <v>60.0472300893551</v>
       </c>
     </row>
     <row r="815" spans="1:4">
@@ -14302,7 +14302,7 @@
         <v>817</v>
       </c>
       <c r="D815">
-        <v>61.54400339993682</v>
+        <v>61.84368773323343</v>
       </c>
     </row>
     <row r="816" spans="1:4">
@@ -14316,7 +14316,7 @@
         <v>818</v>
       </c>
       <c r="D816">
-        <v>62.37901063599286</v>
+        <v>61.92567201670877</v>
       </c>
     </row>
     <row r="817" spans="1:4">
@@ -14330,7 +14330,7 @@
         <v>819</v>
       </c>
       <c r="D817">
-        <v>59.73418161014251</v>
+        <v>59.66780478916508</v>
       </c>
     </row>
     <row r="818" spans="1:4">
@@ -14344,7 +14344,7 @@
         <v>820</v>
       </c>
       <c r="D818">
-        <v>57.10532002513312</v>
+        <v>57.16037791688875</v>
       </c>
     </row>
     <row r="819" spans="1:4">
@@ -14358,7 +14358,7 @@
         <v>821</v>
       </c>
       <c r="D819">
-        <v>55.53225712257375</v>
+        <v>55.79615820617291</v>
       </c>
     </row>
     <row r="820" spans="1:4">
@@ -14372,7 +14372,7 @@
         <v>822</v>
       </c>
       <c r="D820">
-        <v>55.1710781636664</v>
+        <v>54.64606831322272</v>
       </c>
     </row>
     <row r="821" spans="1:4">
@@ -14386,7 +14386,7 @@
         <v>823</v>
       </c>
       <c r="D821">
-        <v>54.59128132978131</v>
+        <v>54.68376999536412</v>
       </c>
     </row>
     <row r="822" spans="1:4">
@@ -14400,7 +14400,7 @@
         <v>824</v>
       </c>
       <c r="D822">
-        <v>50.76911314141653</v>
+        <v>50.86043815906314</v>
       </c>
     </row>
     <row r="823" spans="1:4">
@@ -14414,7 +14414,7 @@
         <v>825</v>
       </c>
       <c r="D823">
-        <v>45.30115145136081</v>
+        <v>45.28851709401708</v>
       </c>
     </row>
     <row r="824" spans="1:4">
@@ -14428,7 +14428,7 @@
         <v>826</v>
       </c>
       <c r="D824">
-        <v>38.79716532615989</v>
+        <v>38.80453135834753</v>
       </c>
     </row>
     <row r="825" spans="1:4">
@@ -14442,7 +14442,7 @@
         <v>827</v>
       </c>
       <c r="D825">
-        <v>32.73673971861474</v>
+        <v>32.56216513878279</v>
       </c>
     </row>
     <row r="826" spans="1:4">
@@ -14456,7 +14456,7 @@
         <v>828</v>
       </c>
       <c r="D826">
-        <v>27.5380258863943</v>
+        <v>27.68223375970436</v>
       </c>
     </row>
     <row r="827" spans="1:4">
@@ -14470,7 +14470,7 @@
         <v>829</v>
       </c>
       <c r="D827">
-        <v>22.23751373218285</v>
+        <v>22.33114531198935</v>
       </c>
     </row>
     <row r="828" spans="1:4">
@@ -14484,7 +14484,7 @@
         <v>830</v>
       </c>
       <c r="D828">
-        <v>18.89257931108279</v>
+        <v>18.69653137750623</v>
       </c>
     </row>
     <row r="829" spans="1:4">
@@ -14498,7 +14498,7 @@
         <v>831</v>
       </c>
       <c r="D829">
-        <v>14.67726116105257</v>
+        <v>14.8529093132343</v>
       </c>
     </row>
     <row r="830" spans="1:4">
@@ -14512,7 +14512,7 @@
         <v>832</v>
       </c>
       <c r="D830">
-        <v>11.80931891100816</v>
+        <v>11.93737215295884</v>
       </c>
     </row>
     <row r="831" spans="1:4">
@@ -14526,7 +14526,7 @@
         <v>833</v>
       </c>
       <c r="D831">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="832" spans="1:4">
@@ -14540,7 +14540,7 @@
         <v>834</v>
       </c>
       <c r="D832">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="833" spans="1:4">
@@ -14554,7 +14554,7 @@
         <v>835</v>
       </c>
       <c r="D833">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="834" spans="1:4">
@@ -14568,7 +14568,7 @@
         <v>836</v>
       </c>
       <c r="D834">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="835" spans="1:4">
@@ -14582,7 +14582,7 @@
         <v>837</v>
       </c>
       <c r="D835">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
     <row r="836" spans="1:4">
@@ -14596,7 +14596,7 @@
         <v>838</v>
       </c>
       <c r="D836">
-        <v>10.15805966694125</v>
+        <v>10.23741880341881</v>
       </c>
     </row>
   </sheetData>
